--- a/jacky_code/Matlab_data/FullPower_BeamShutdownSweep_GS01_U70_P03S49_UserSatisfaction_CDF_3MethodCompare.xlsx
+++ b/jacky_code/Matlab_data/FullPower_BeamShutdownSweep_GS01_U70_P03S49_UserSatisfaction_CDF_3MethodCompare.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="646" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1292" uniqueCount="17">
   <si>
     <t>method</t>
   </si>

--- a/jacky_code/Matlab_data/FullPower_BeamShutdownSweep_GS01_U70_P03S49_UserSatisfaction_CDF_3MethodCompare.xlsx
+++ b/jacky_code/Matlab_data/FullPower_BeamShutdownSweep_GS01_U70_P03S49_UserSatisfaction_CDF_3MethodCompare.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1292" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="2584" uniqueCount="19">
   <si>
     <t>method</t>
   </si>
@@ -66,6 +66,12 @@
   <si>
     <t>max_satisfaction</t>
   </si>
+  <si>
+    <t>Only HBR</t>
+  </si>
+  <si>
+    <t>EABR</t>
+  </si>
 </sst>
 </file>
 
@@ -113,12 +119,12 @@
   <dimension ref="A1:F208"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.21875" customWidth="true"/>
-    <col min="2" max="2" width="14.88671875" customWidth="true"/>
-    <col min="3" max="3" width="13.5546875" customWidth="true"/>
-    <col min="4" max="4" width="18.5546875" customWidth="true"/>
-    <col min="5" max="5" width="7.21875" customWidth="true"/>
-    <col min="6" max="6" width="13.5546875" customWidth="true"/>
+    <col min="1" max="1" width="9.28515625" customWidth="true"/>
+    <col min="2" max="2" width="16.140625" customWidth="true"/>
+    <col min="3" max="3" width="13.7109375" customWidth="true"/>
+    <col min="4" max="4" width="18.85546875" customWidth="true"/>
+    <col min="5" max="5" width="8" customWidth="true"/>
+    <col min="6" max="6" width="14.85546875" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1523,7 +1529,7 @@
     </row>
     <row r="71">
       <c r="A71" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B71" s="0">
         <v>0</v>
@@ -1543,7 +1549,7 @@
     </row>
     <row r="72">
       <c r="A72" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B72" s="0">
         <v>0</v>
@@ -1563,7 +1569,7 @@
     </row>
     <row r="73">
       <c r="A73" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B73" s="0">
         <v>0.20956854672269118</v>
@@ -1583,7 +1589,7 @@
     </row>
     <row r="74">
       <c r="A74" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B74" s="0">
         <v>0.21063152568803922</v>
@@ -1603,7 +1609,7 @@
     </row>
     <row r="75">
       <c r="A75" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B75" s="0">
         <v>0.21243642879025576</v>
@@ -1623,7 +1629,7 @@
     </row>
     <row r="76">
       <c r="A76" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B76" s="0">
         <v>0.21261311439541486</v>
@@ -1643,7 +1649,7 @@
     </row>
     <row r="77">
       <c r="A77" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B77" s="0">
         <v>0.23236779284708028</v>
@@ -1663,7 +1669,7 @@
     </row>
     <row r="78">
       <c r="A78" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B78" s="0">
         <v>0.2345539468736822</v>
@@ -1683,7 +1689,7 @@
     </row>
     <row r="79">
       <c r="A79" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B79" s="0">
         <v>0.23668389981207055</v>
@@ -1703,7 +1709,7 @@
     </row>
     <row r="80">
       <c r="A80" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B80" s="0">
         <v>0.24079983614511258</v>
@@ -1723,7 +1729,7 @@
     </row>
     <row r="81">
       <c r="A81" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B81" s="0">
         <v>0.24190016010545964</v>
@@ -1743,7 +1749,7 @@
     </row>
     <row r="82">
       <c r="A82" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B82" s="0">
         <v>0.25071869321400636</v>
@@ -1763,7 +1769,7 @@
     </row>
     <row r="83">
       <c r="A83" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B83" s="0">
         <v>0.25901073179553563</v>
@@ -1783,7 +1789,7 @@
     </row>
     <row r="84">
       <c r="A84" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B84" s="0">
         <v>0.26630218651998516</v>
@@ -1803,7 +1809,7 @@
     </row>
     <row r="85">
       <c r="A85" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B85" s="0">
         <v>0.26697921280209985</v>
@@ -1823,7 +1829,7 @@
     </row>
     <row r="86">
       <c r="A86" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B86" s="0">
         <v>0.27600968530667069</v>
@@ -1843,7 +1849,7 @@
     </row>
     <row r="87">
       <c r="A87" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B87" s="0">
         <v>0.2863370598289246</v>
@@ -1863,7 +1869,7 @@
     </row>
     <row r="88">
       <c r="A88" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B88" s="0">
         <v>0.28891661738358188</v>
@@ -1883,7 +1889,7 @@
     </row>
     <row r="89">
       <c r="A89" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B89" s="0">
         <v>0.30224683897032079</v>
@@ -1903,7 +1909,7 @@
     </row>
     <row r="90">
       <c r="A90" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B90" s="0">
         <v>0.33724423032909084</v>
@@ -1923,7 +1929,7 @@
     </row>
     <row r="91">
       <c r="A91" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B91" s="0">
         <v>0.34312385258814421</v>
@@ -1943,7 +1949,7 @@
     </row>
     <row r="92">
       <c r="A92" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B92" s="0">
         <v>0.36133702298731585</v>
@@ -1963,7 +1969,7 @@
     </row>
     <row r="93">
       <c r="A93" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B93" s="0">
         <v>0.37026597838788744</v>
@@ -1983,7 +1989,7 @@
     </row>
     <row r="94">
       <c r="A94" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B94" s="0">
         <v>0.37028671173727262</v>
@@ -2003,7 +2009,7 @@
     </row>
     <row r="95">
       <c r="A95" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B95" s="0">
         <v>0.37228900590103792</v>
@@ -2023,7 +2029,7 @@
     </row>
     <row r="96">
       <c r="A96" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B96" s="0">
         <v>0.37574088089911517</v>
@@ -2043,7 +2049,7 @@
     </row>
     <row r="97">
       <c r="A97" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B97" s="0">
         <v>0.38368465210244745</v>
@@ -2063,7 +2069,7 @@
     </row>
     <row r="98">
       <c r="A98" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B98" s="0">
         <v>0.3886238995439763</v>
@@ -2083,7 +2089,7 @@
     </row>
     <row r="99">
       <c r="A99" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B99" s="0">
         <v>0.39898788622532833</v>
@@ -2103,7 +2109,7 @@
     </row>
     <row r="100">
       <c r="A100" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B100" s="0">
         <v>0.4068312523014288</v>
@@ -2123,7 +2129,7 @@
     </row>
     <row r="101">
       <c r="A101" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B101" s="0">
         <v>0.41065414776178039</v>
@@ -2143,7 +2149,7 @@
     </row>
     <row r="102">
       <c r="A102" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B102" s="0">
         <v>0.41178163889795899</v>
@@ -2163,7 +2169,7 @@
     </row>
     <row r="103">
       <c r="A103" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B103" s="0">
         <v>0.41332192748881086</v>
@@ -2183,7 +2189,7 @@
     </row>
     <row r="104">
       <c r="A104" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B104" s="0">
         <v>0.42090251709188264</v>
@@ -2203,7 +2209,7 @@
     </row>
     <row r="105">
       <c r="A105" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B105" s="0">
         <v>0.43594018116989192</v>
@@ -2223,7 +2229,7 @@
     </row>
     <row r="106">
       <c r="A106" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B106" s="0">
         <v>0.45073938406472946</v>
@@ -2243,7 +2249,7 @@
     </row>
     <row r="107">
       <c r="A107" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B107" s="0">
         <v>0.45211519122680294</v>
@@ -2263,7 +2269,7 @@
     </row>
     <row r="108">
       <c r="A108" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B108" s="0">
         <v>0.45427203081127537</v>
@@ -2283,7 +2289,7 @@
     </row>
     <row r="109">
       <c r="A109" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B109" s="0">
         <v>0.47344765839131564</v>
@@ -2303,7 +2309,7 @@
     </row>
     <row r="110">
       <c r="A110" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B110" s="0">
         <v>0.48093671392617343</v>
@@ -2323,7 +2329,7 @@
     </row>
     <row r="111">
       <c r="A111" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B111" s="0">
         <v>0.49430617945530209</v>
@@ -2343,7 +2349,7 @@
     </row>
     <row r="112">
       <c r="A112" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B112" s="0">
         <v>0.50201974261380788</v>
@@ -2363,7 +2369,7 @@
     </row>
     <row r="113">
       <c r="A113" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B113" s="0">
         <v>0.5219607828456907</v>
@@ -2383,7 +2389,7 @@
     </row>
     <row r="114">
       <c r="A114" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B114" s="0">
         <v>0.58411728888479864</v>
@@ -2403,7 +2409,7 @@
     </row>
     <row r="115">
       <c r="A115" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B115" s="0">
         <v>0.58830399604913852</v>
@@ -2423,7 +2429,7 @@
     </row>
     <row r="116">
       <c r="A116" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B116" s="0">
         <v>0.5897564030489818</v>
@@ -2443,7 +2449,7 @@
     </row>
     <row r="117">
       <c r="A117" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B117" s="0">
         <v>0.61837386000800587</v>
@@ -2463,7 +2469,7 @@
     </row>
     <row r="118">
       <c r="A118" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B118" s="0">
         <v>0.62613517785312223</v>
@@ -2483,7 +2489,7 @@
     </row>
     <row r="119">
       <c r="A119" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B119" s="0">
         <v>0.6833446800568731</v>
@@ -2503,7 +2509,7 @@
     </row>
     <row r="120">
       <c r="A120" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B120" s="0">
         <v>0.68944670217496007</v>
@@ -2523,7 +2529,7 @@
     </row>
     <row r="121">
       <c r="A121" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B121" s="0">
         <v>0.71864982929451404</v>
@@ -2543,7 +2549,7 @@
     </row>
     <row r="122">
       <c r="A122" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B122" s="0">
         <v>0.72170367141065905</v>
@@ -2563,7 +2569,7 @@
     </row>
     <row r="123">
       <c r="A123" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B123" s="0">
         <v>0.73783482238131315</v>
@@ -2583,7 +2589,7 @@
     </row>
     <row r="124">
       <c r="A124" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B124" s="0">
         <v>0.74706024489298428</v>
@@ -2603,7 +2609,7 @@
     </row>
     <row r="125">
       <c r="A125" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B125" s="0">
         <v>0.76500664151604825</v>
@@ -2623,7 +2629,7 @@
     </row>
     <row r="126">
       <c r="A126" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B126" s="0">
         <v>0.77348048082901988</v>
@@ -2643,7 +2649,7 @@
     </row>
     <row r="127">
       <c r="A127" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B127" s="0">
         <v>0.78938005144077583</v>
@@ -2663,7 +2669,7 @@
     </row>
     <row r="128">
       <c r="A128" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B128" s="0">
         <v>0.79514184434473512</v>
@@ -2683,7 +2689,7 @@
     </row>
     <row r="129">
       <c r="A129" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B129" s="0">
         <v>0.8099584117306321</v>
@@ -2703,7 +2709,7 @@
     </row>
     <row r="130">
       <c r="A130" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B130" s="0">
         <v>0.850217613250974</v>
@@ -2723,7 +2729,7 @@
     </row>
     <row r="131">
       <c r="A131" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B131" s="0">
         <v>0.86165370544549413</v>
@@ -2743,7 +2749,7 @@
     </row>
     <row r="132">
       <c r="A132" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B132" s="0">
         <v>0.88111290205971915</v>
@@ -2763,7 +2769,7 @@
     </row>
     <row r="133">
       <c r="A133" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B133" s="0">
         <v>1</v>
@@ -2783,7 +2789,7 @@
     </row>
     <row r="134">
       <c r="A134" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B134" s="0">
         <v>1</v>
@@ -2803,7 +2809,7 @@
     </row>
     <row r="135">
       <c r="A135" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B135" s="0">
         <v>1</v>
@@ -2823,7 +2829,7 @@
     </row>
     <row r="136">
       <c r="A136" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B136" s="0">
         <v>1</v>
@@ -2843,7 +2849,7 @@
     </row>
     <row r="137">
       <c r="A137" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B137" s="0">
         <v>1</v>
@@ -2863,7 +2869,7 @@
     </row>
     <row r="138">
       <c r="A138" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B138" s="0">
         <v>1</v>
@@ -2883,7 +2889,7 @@
     </row>
     <row r="139">
       <c r="A139" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B139" s="0">
         <v>1</v>
@@ -2903,7 +2909,7 @@
     </row>
     <row r="140">
       <c r="A140" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B140" s="0">
         <v>0.35011010423605071</v>
@@ -2923,7 +2929,7 @@
     </row>
     <row r="141">
       <c r="A141" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B141" s="0">
         <v>0.35278180819272442</v>
@@ -2943,7 +2949,7 @@
     </row>
     <row r="142">
       <c r="A142" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B142" s="0">
         <v>0.35458209097204085</v>
@@ -2963,7 +2969,7 @@
     </row>
     <row r="143">
       <c r="A143" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B143" s="0">
         <v>0.35922509411875042</v>
@@ -2983,7 +2989,7 @@
     </row>
     <row r="144">
       <c r="A144" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B144" s="0">
         <v>0.38519122719107429</v>
@@ -3003,7 +3009,7 @@
     </row>
     <row r="145">
       <c r="A145" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B145" s="0">
         <v>0.38908223284497823</v>
@@ -3023,7 +3029,7 @@
     </row>
     <row r="146">
       <c r="A146" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B146" s="0">
         <v>0.39554523603025693</v>
@@ -3043,7 +3049,7 @@
     </row>
     <row r="147">
       <c r="A147" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B147" s="0">
         <v>0.39582563885266259</v>
@@ -3063,7 +3069,7 @@
     </row>
     <row r="148">
       <c r="A148" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B148" s="0">
         <v>0.40168891560138564</v>
@@ -3083,7 +3089,7 @@
     </row>
     <row r="149">
       <c r="A149" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B149" s="0">
         <v>0.41641724203273262</v>
@@ -3103,7 +3109,7 @@
     </row>
     <row r="150">
       <c r="A150" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B150" s="0">
         <v>0.42864812510330852</v>
@@ -3123,7 +3129,7 @@
     </row>
     <row r="151">
       <c r="A151" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B151" s="0">
         <v>0.43167043694845331</v>
@@ -3143,7 +3149,7 @@
     </row>
     <row r="152">
       <c r="A152" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B152" s="0">
         <v>0.4393431107572569</v>
@@ -3163,7 +3169,7 @@
     </row>
     <row r="153">
       <c r="A153" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B153" s="0">
         <v>0.44441116541295211</v>
@@ -3183,7 +3189,7 @@
     </row>
     <row r="154">
       <c r="A154" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B154" s="0">
         <v>0.46845062814162403</v>
@@ -3203,7 +3209,7 @@
     </row>
     <row r="155">
       <c r="A155" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B155" s="0">
         <v>0.47216941047643912</v>
@@ -3223,7 +3229,7 @@
     </row>
     <row r="156">
       <c r="A156" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B156" s="0">
         <v>0.49128520179177143</v>
@@ -3243,7 +3249,7 @@
     </row>
     <row r="157">
       <c r="A157" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B157" s="0">
         <v>0.52870789597060042</v>
@@ -3263,7 +3269,7 @@
     </row>
     <row r="158">
       <c r="A158" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B158" s="0">
         <v>0.56265734332873141</v>
@@ -3283,7 +3289,7 @@
     </row>
     <row r="159">
       <c r="A159" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B159" s="0">
         <v>0.59047901526940616</v>
@@ -3303,7 +3309,7 @@
     </row>
     <row r="160">
       <c r="A160" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B160" s="0">
         <v>0.59386295007781942</v>
@@ -3323,7 +3329,7 @@
     </row>
     <row r="161">
       <c r="A161" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B161" s="0">
         <v>0.5970239635509561</v>
@@ -3343,7 +3349,7 @@
     </row>
     <row r="162">
       <c r="A162" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B162" s="0">
         <v>0.60167752039955436</v>
@@ -3363,7 +3369,7 @@
     </row>
     <row r="163">
       <c r="A163" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B163" s="0">
         <v>0.60170710845990927</v>
@@ -3383,7 +3389,7 @@
     </row>
     <row r="164">
       <c r="A164" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B164" s="0">
         <v>0.60456299621181675</v>
@@ -3403,7 +3409,7 @@
     </row>
     <row r="165">
       <c r="A165" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B165" s="0">
         <v>0.62541188476033416</v>
@@ -3423,7 +3429,7 @@
     </row>
     <row r="166">
       <c r="A166" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B166" s="0">
         <v>0.62774945985658204</v>
@@ -3443,7 +3449,7 @@
     </row>
     <row r="167">
       <c r="A167" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B167" s="0">
         <v>0.63882153785507401</v>
@@ -3463,7 +3469,7 @@
     </row>
     <row r="168">
       <c r="A168" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B168" s="0">
         <v>0.65871333105148111</v>
@@ -3483,7 +3489,7 @@
     </row>
     <row r="169">
       <c r="A169" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B169" s="0">
         <v>0.66028883886101664</v>
@@ -3503,7 +3509,7 @@
     </row>
     <row r="170">
       <c r="A170" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B170" s="0">
         <v>0.66243975104095398</v>
@@ -3523,7 +3529,7 @@
     </row>
     <row r="171">
       <c r="A171" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B171" s="0">
         <v>0.66298671799445985</v>
@@ -3543,7 +3549,7 @@
     </row>
     <row r="172">
       <c r="A172" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B172" s="0">
         <v>0.67477192702062672</v>
@@ -3563,7 +3569,7 @@
     </row>
     <row r="173">
       <c r="A173" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B173" s="0">
         <v>0.67865088955571662</v>
@@ -3583,7 +3589,7 @@
     </row>
     <row r="174">
       <c r="A174" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B174" s="0">
         <v>0.68138068216728243</v>
@@ -3603,7 +3609,7 @@
     </row>
     <row r="175">
       <c r="A175" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B175" s="0">
         <v>0.69428568553228076</v>
@@ -3623,7 +3629,7 @@
     </row>
     <row r="176">
       <c r="A176" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B176" s="0">
         <v>0.70552855320185204</v>
@@ -3643,7 +3649,7 @@
     </row>
     <row r="177">
       <c r="A177" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B177" s="0">
         <v>0.71490166865479265</v>
@@ -3663,7 +3669,7 @@
     </row>
     <row r="178">
       <c r="A178" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B178" s="0">
         <v>0.75095024810703648</v>
@@ -3683,7 +3689,7 @@
     </row>
     <row r="179">
       <c r="A179" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B179" s="0">
         <v>0.7608676451601174</v>
@@ -3703,7 +3709,7 @@
     </row>
     <row r="180">
       <c r="A180" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B180" s="0">
         <v>0.78635444791178244</v>
@@ -3723,7 +3729,7 @@
     </row>
     <row r="181">
       <c r="A181" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B181" s="0">
         <v>0.90750766203069744</v>
@@ -3743,7 +3749,7 @@
     </row>
     <row r="182">
       <c r="A182" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B182" s="0">
         <v>0.91307464962743479</v>
@@ -3763,7 +3769,7 @@
     </row>
     <row r="183">
       <c r="A183" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B183" s="0">
         <v>0.91628748780389202</v>
@@ -3783,7 +3789,7 @@
     </row>
     <row r="184">
       <c r="A184" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B184" s="0">
         <v>0.93609772930931956</v>
@@ -3803,7 +3809,7 @@
     </row>
     <row r="185">
       <c r="A185" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B185" s="0">
         <v>0.98564046226861735</v>
@@ -3823,7 +3829,7 @@
     </row>
     <row r="186">
       <c r="A186" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B186" s="0">
         <v>1</v>
@@ -3843,7 +3849,7 @@
     </row>
     <row r="187">
       <c r="A187" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B187" s="0">
         <v>1</v>
@@ -3863,7 +3869,7 @@
     </row>
     <row r="188">
       <c r="A188" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B188" s="0">
         <v>1</v>
@@ -3883,7 +3889,7 @@
     </row>
     <row r="189">
       <c r="A189" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B189" s="0">
         <v>1</v>
@@ -3903,7 +3909,7 @@
     </row>
     <row r="190">
       <c r="A190" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B190" s="0">
         <v>1</v>
@@ -3923,7 +3929,7 @@
     </row>
     <row r="191">
       <c r="A191" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B191" s="0">
         <v>1</v>
@@ -3943,7 +3949,7 @@
     </row>
     <row r="192">
       <c r="A192" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B192" s="0">
         <v>1</v>
@@ -3963,7 +3969,7 @@
     </row>
     <row r="193">
       <c r="A193" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B193" s="0">
         <v>1</v>
@@ -3983,7 +3989,7 @@
     </row>
     <row r="194">
       <c r="A194" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B194" s="0">
         <v>1</v>
@@ -4003,7 +4009,7 @@
     </row>
     <row r="195">
       <c r="A195" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B195" s="0">
         <v>1</v>
@@ -4023,7 +4029,7 @@
     </row>
     <row r="196">
       <c r="A196" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B196" s="0">
         <v>1</v>
@@ -4043,7 +4049,7 @@
     </row>
     <row r="197">
       <c r="A197" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B197" s="0">
         <v>1</v>
@@ -4063,7 +4069,7 @@
     </row>
     <row r="198">
       <c r="A198" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B198" s="0">
         <v>1</v>
@@ -4083,7 +4089,7 @@
     </row>
     <row r="199">
       <c r="A199" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B199" s="0">
         <v>1</v>
@@ -4103,7 +4109,7 @@
     </row>
     <row r="200">
       <c r="A200" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B200" s="0">
         <v>1</v>
@@ -4123,7 +4129,7 @@
     </row>
     <row r="201">
       <c r="A201" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B201" s="0">
         <v>1</v>
@@ -4143,7 +4149,7 @@
     </row>
     <row r="202">
       <c r="A202" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B202" s="0">
         <v>1</v>
@@ -4163,7 +4169,7 @@
     </row>
     <row r="203">
       <c r="A203" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B203" s="0">
         <v>1</v>
@@ -4183,7 +4189,7 @@
     </row>
     <row r="204">
       <c r="A204" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B204" s="0">
         <v>1</v>
@@ -4203,7 +4209,7 @@
     </row>
     <row r="205">
       <c r="A205" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B205" s="0">
         <v>1</v>
@@ -4223,7 +4229,7 @@
     </row>
     <row r="206">
       <c r="A206" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B206" s="0">
         <v>1</v>
@@ -4243,7 +4249,7 @@
     </row>
     <row r="207">
       <c r="A207" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B207" s="0">
         <v>1</v>
@@ -4263,7 +4269,7 @@
     </row>
     <row r="208">
       <c r="A208" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B208" s="0">
         <v>1</v>
@@ -4290,16 +4296,16 @@
   <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.21875" customWidth="true"/>
-    <col min="2" max="2" width="7.21875" customWidth="true"/>
-    <col min="3" max="3" width="9.44140625" customWidth="true"/>
-    <col min="4" max="4" width="14.21875" customWidth="true"/>
-    <col min="5" max="5" width="17.44140625" customWidth="true"/>
-    <col min="6" max="6" width="20.77734375" customWidth="true"/>
-    <col min="7" max="7" width="21.5546875" customWidth="true"/>
-    <col min="8" max="8" width="14.88671875" customWidth="true"/>
-    <col min="9" max="9" width="18.5546875" customWidth="true"/>
-    <col min="10" max="10" width="13.5546875" customWidth="true"/>
+    <col min="1" max="1" width="9.28515625" customWidth="true"/>
+    <col min="2" max="2" width="8" customWidth="true"/>
+    <col min="3" max="3" width="10.28515625" customWidth="true"/>
+    <col min="4" max="4" width="15.28515625" customWidth="true"/>
+    <col min="5" max="5" width="19" customWidth="true"/>
+    <col min="6" max="6" width="22" customWidth="true"/>
+    <col min="7" max="7" width="22.85546875" customWidth="true"/>
+    <col min="8" max="8" width="16" customWidth="true"/>
+    <col min="9" max="9" width="18.85546875" customWidth="true"/>
+    <col min="10" max="10" width="14.85546875" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4368,7 +4374,7 @@
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B3" s="0">
         <v>69</v>
@@ -4400,7 +4406,7 @@
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B4" s="0">
         <v>69</v>
